--- a/docs/Requirements/Requirements Traceability Matrix/Requirements_Traceability_Matrix_v0.11.xlsx
+++ b/docs/Requirements/Requirements Traceability Matrix/Requirements_Traceability_Matrix_v0.11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elind\m4-wt\records\docs\Requirements\Requirements Traceability Matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3049B722-EF20-43C4-9DA6-70B721CA50C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EBBD59-0368-4C42-ADC6-BA0147F3DEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RTM v0.11" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="991">
   <si>
     <t>Requirements Traceability Matrix</t>
   </si>
@@ -2071,12 +2071,6 @@
     <t>Tested: E2E-6, E2E-13.</t>
   </si>
   <si>
-    <t>Built; verification on staging pending: the four role journeys are built (E2E-1 to E2E-13 on the test cluster).</t>
-  </si>
-  <si>
-    <t>Not yet verified [pending RC].</t>
-  </si>
-  <si>
     <t>Partially implemented: authentication attempts and refused operations are written to auditLog by the application; transitions and assignments rely on the Atlas trigger (PR #136: a7053fb).</t>
   </si>
   <si>
@@ -2092,24 +2086,12 @@
     <t>Tested: tests/app.test.js, tests/release.test.js.</t>
   </si>
   <si>
-    <t>Measurement prepared, not run: server-side submission timing script (perf/, c858788).</t>
-  </si>
-  <si>
     <t>Not measured.</t>
   </si>
   <si>
-    <t>Partially implemented: standard-journey load script (perf/, c858788).</t>
-  </si>
-  <si>
-    <t>Built; verification on staging pending: passwords are stored as scrypt hashes (DEC-018 §2).</t>
-  </si>
-  <si>
     <t>Tested: tests/passwordHasher.test.js, tests/userInitialPassword.test.js; NV-147.</t>
   </si>
   <si>
-    <t>Partially implemented: HTTPS on staging (Nginx, self-signed certificate).</t>
-  </si>
-  <si>
     <t>Implemented: the server refuses an operation a role may not perform on every route, whatever the client sends (DEC-012 points 1 and 2) (PR #136: a7053fb, 804138f).</t>
   </si>
   <si>
@@ -2152,9 +2134,6 @@
     <t>Not met under the amended NFR-2.6 (CR-004): indexes declared in src/models and the data baseline index table (DB-01 v0.3).</t>
   </si>
   <si>
-    <t>Built; verification on staging pending: sessions are stored in MongoDB, not in process memory (DEC-018).</t>
-  </si>
-  <si>
     <t>Not evidenced on the M0 tier.</t>
   </si>
   <si>
@@ -2701,18 +2680,9 @@
     <t>Met (frozen build 6408ab7). E2E-6 on arrival and E2E-13 after each of ten Requester and Technician interactions, in four browsers. Only 360 px is measured.</t>
   </si>
   <si>
-    <t>Staging check at the RC [pending RC].</t>
-  </si>
-  <si>
     <t>From AC-NFR-1.3: all four journeys complete successfully.</t>
   </si>
   <si>
-    <t>[pending RC].</t>
-  </si>
-  <si>
-    <t>Not Met (frozen build 6408ab7) until the staging walkthrough of the four journeys at the RC.</t>
-  </si>
-  <si>
     <t>tests/authService.test.js; tests/refusalRecording.test.js.</t>
   </si>
   <si>
@@ -2743,9 +2713,6 @@
     <t>From AC-NFR-2.1: at least 95 confirmations are returned within 3 seconds, measured server-side.</t>
   </si>
   <si>
-    <t>Not Met (frozen build 6408ab7) until the NFR-2.1 run on staging [pending RC].</t>
-  </si>
-  <si>
     <t>From AC-NFR-2.2: at least 95 return within 2 seconds.</t>
   </si>
   <si>
@@ -2761,12 +2728,6 @@
     <t>From AC-NFR-2.4: no request failed and no unhandled server error was recorded.</t>
   </si>
   <si>
-    <t>M3 staging run (docs/evidence/M3-perf/NFR-2.4_load_run_2026-10-15.txt); [pending RC].</t>
-  </si>
-  <si>
-    <t>Partially Met (frozen build 6408ab7): passed at M3 (login, read, transition); the re-run at the RC with submission and lists [pending RC].</t>
-  </si>
-  <si>
     <t>From AC-NFR-2.5: the result is at least 99%.</t>
   </si>
   <si>
@@ -2779,18 +2740,9 @@
     <t>From AC-NFR-3.1: the password appears only as a salted hash from a recognised slow hashing function and the plaintext appears nowhere.</t>
   </si>
   <si>
-    <t>npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-147 (docs/evidence/M4-build/); [pending RC].</t>
-  </si>
-  <si>
-    <t>Not Met (frozen build 6408ab7) until the inspection of users, logs and backups on staging [pending RC].</t>
-  </si>
-  <si>
     <t>From AC-NFR-3.2: the connection is refused or redirected to TLS 1.2 or higher.</t>
   </si>
   <si>
-    <t>Partially Met (frozen build 6408ab7): HTTPS in use; the HTTP 301 and the refusal of TLS below 1.2 [pending RC].</t>
-  </si>
-  <si>
     <t>E2E-2a; E2E-2b; integration cases (tests/integration/); tests/authorisationGuard.test.js; tests/openapiRoutes.test.js.</t>
   </si>
   <si>
@@ -2860,12 +2812,6 @@
     <t>From AC-NFR-1.11: each operation has one structured entry recording operation, duration in milliseconds and outcome, and no entry contains a name, e-mail address, student number or free-text description.</t>
   </si>
   <si>
-    <t>npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-140, NV-167 (docs/evidence/M4-build/); [pending RC].</t>
-  </si>
-  <si>
-    <t>Partially Met (frozen build 6408ab7): shown over HTTP; under load on the deployed system with the log retrieved [pending RC]. DEF-029 (errors logged as "POST /") fixed.</t>
-  </si>
-  <si>
     <t>document check 17/10/2026: 21 declared indexes against DB-01 v0.3.</t>
   </si>
   <si>
@@ -2878,12 +2824,6 @@
     <t>From AC-NFR-2.7: no user session state is held in process memory and no query plan contains a full-table scan on the request or audit tables.</t>
   </si>
   <si>
-    <t>npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; [pending RC].</t>
-  </si>
-  <si>
-    <t>Not Met (frozen build 6408ab7) until explain() and the process-memory check on staging [pending RC].</t>
-  </si>
-  <si>
     <t>From AC-NFR-3.7: the personal information is not readable as plaintext.</t>
   </si>
   <si>
@@ -2893,9 +2833,6 @@
     <t>From AC-NFR-4.1: every field maps to at least one of those purposes and no field maps to none.</t>
   </si>
   <si>
-    <t>Not Met (frozen build 6408ab7) until the field-to-purpose review against DEC-017 [pending RC].</t>
-  </si>
-  <si>
     <t>From AC-NFR-4.2: every field listed in REQUEST_PERSONAL_FIELDS and HISTORY_PERSONAL_FIELDS is null, anonymisedAt is set, no notification for it remains, and the FR-8.1 and FR-8.2 counts are identical to those recorded before anonymisation.</t>
   </si>
   <si>
@@ -2971,16 +2908,109 @@
     <t>DEC-005; CFL-004; RSK-002; OI-12; DEC-017; PROC-001; CR-002 (approved 17/10/2026)</t>
   </si>
   <si>
-    <t>Live artefact, version 0.9 at Milestone 3. Source, requirement and acceptance criteria were populated at M1. The ASR, architecture, data, design, technology, implementation and verification columns were introduced at M2: populated where M2 evidence exists, and carried at a controlled status where it legitimately does not. v0.5 (29/09/2026, R. van der Merwe): data/persistence column completed for all 79 rows; DEC-015 to DEC-017 and CR-001 to CR-004 referenced. Change notes: RTM_v0.5_Change_Notes.md. v0.6 (30/09/2026, C. Burger): ASR / quality-driver link and Architecture / module / component columns completed for all 79 rows from PED §6A (ASR-01 to ASR-06, DEC-014); requirements with no driver are marked explicitly. v0.7 (30/09/2026, R. van der Merwe): Implementation and Verification evidence populated for the 11 requirements the application slice now implements (FR-1.3, FR-1.5, FR-2.2, FR-3.5, FR-6.1 to FR-6.7), after PR #63; FR-1.5, FR-2.2 and FR-3.5 are recorded as partial. Status column unchanged. v0.8 (30/09/2026, E. Lindsay): NFR-3.3 Implementation and Verification evidence added; FR-1.3 and FR-6.7 corrected from Implemented to Partially implemented (AC-FR-1.3 rejected-attempt recording not built; DB-01 layer 3 is M3). Status column unchanged. v0.9 (11/10/2026, E. Lindsay): Implementation and Verification evidence added for FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 after the M3 Phase 0 composition root (PR #83, DEC-018); FR-1.1, FR-1.4 and NFR-1.4 recorded as partial. Design / interface entries for DEC-018 added on the same five rows. The application is reachable over HTTP against the Atlas test cluster (SMOKE-01); no index is evidenced on the cluster. Status column unchanged. Also corrected in v0.9: the NFR-3.4 Data/persistence cell, which said the TTL index enforces idle expiry — DB-01 v0.3 §3.9 states that reading is wrong, and the enforcement is in the application against lastSeenAt (R. van der Merwe's column, corrected by E. Lindsay and notified). The Architecture column on FR-1.4, NFR-1.6 and NFR-3.4 changed from "(planned)" to reflect the composed application (C. Burger's column, corrected by E. Lindsay and notified). NOTE ON EVIDENCE: Implementation and verification evidence is recorded at component level. Each component named is implemented and verified by npm test, with its collaborators substituted (no database, no HTTP). Since v0.9 the composition root (src/composition.js, src/server.js) composes the routes, services, repositories and unit of work, and the session middleware sets req.actor; the application is reachable over HTTP against the Atlas test cluster, recorded in docs/evidence/M3-P0/SMOKE-01_phase0_reachability.txt. SMOKE-01 is reachability evidence only: it does not show that any index exists on the cluster. Where a row cites SMOKE-01, that check ran against the cluster; every other cited test ran without a database. Verification that needs a live database (transaction atomicity and rollback, DB-01 layer 3, audit-trigger lag) is M3. v0.10 (15/10/2026, E. Lindsay): the M3 chain added as four columns (O test cases, P expected result, Q execution evidence, R defect / M3 status), populated for the 27 requirements the M3 release candidate (v3.0-M3-rc) implements or verifies; the other 52 rows are marked "Not in M3 scope" with the reason. Unit evidence is the CI run at the release candidate (Node 22); test evidence records UT-1 to UT-5 and BB-1 to BB-5 (M3_Test_Evidence_Records_v0.1.md); API cases on the test cluster; E2E at v3.0-M3-rc; staging, NFR-2.4 and smoke from the staging deploy record. Defects and debt cited: DEF-011, DEF-019, DEF-020, TD-005, TD-006, TD-008; open items OI-01, OI-15, OI-16, OI-17, OI-18. Columns A to N and the Status summary sheet unchanged. v0.11 (17/10/2026, E. Lindsay): final M4 status for all 79 requirement rows (80 acceptance criteria; FR-2.2 holds AC-FR-2.2a and AC-FR-2.2b in one row, each given its own status) at the frozen build 6408ab7 (PR #136), counted under the strict rule (Met only where the Then clause is shown through the system's own interface): 56 Met, 9 Partially Met, 15 Not Met, 60.5 of 80. Columns K, L, O, P, Q and R rewritten for every row from the M4 build and its evidence (unit tests, API integration run 3, E2E run 2 in four browsers, NV-101 to NV-173); cells that depend on the RC on staging read [pending RC]. CR-001 to CR-004 approved 17/10/2026 by the team, not validated with a client stakeholder: C77, E75, E77, E81, H77, M58, N35, N40, N58, N74, N75, N77, N81 and P75 updated. Defects fixed in the M4 build and cited: DEF-007 to DEF-012 and DEF-022 to DEF-031 (DEF-031: the category name shown as "Request" after a sign-in on the request page). Columns A to J other than C77, E75, E77, E81 and H77 unchanged. The sheet is renamed "RTM v0.11"; the headers of O, Q and R read (M4); the Status summary is updated (A1, B9 to C10, D9, D10).</t>
-  </si>
-  <si>
     <t>Column completeness at v0.11</t>
   </si>
   <si>
-    <t>v0.7 (Robert): 11 rows populated from the application slice after PR #63. v0.8 (Ethan): NFR-3.3 added; FR-1.3 and FR-6.7 corrected to partial. v0.9 (Ethan): FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 added after PR #83. 17 rows populated (8 implemented, 9 partial). Remaining 62: all three members, criterion F, as code is written v0.11 (Ethan): rewritten for all 79 rows from the M4 build at the frozen build 6408ab7 (PR #136); every row has an entry, including the rows not implemented, so 79 populated and 0 outstanding. Rows whose evidence is the release candidate on staging say [pending RC].</t>
-  </si>
-  <si>
-    <t>v0.7 (Robert): 11 rows with automated test evidence (npm test 80/80). v0.8 (Ethan): NFR-3.3 added; 12 rows. v0.9 (Ethan): FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 added (npm test 132/132; SMOKE-01 against the Atlas test cluster for reachability); 17 rows. Remaining 62 and live-cluster verification beyond reachability: M3 v0.11 (Ethan): rewritten for all 79 rows with the M4 evidence at 6408ab7: npm test 459 tests (451 pass, 0 fail, 8 skipped), integration 40 of 40 on the test cluster, E2E 56 of 56 in four browsers; 79 populated, 0 outstanding. Rows whose evidence is the RC on staging say [pending RC].</t>
+    <t>Live artefact, version 0.9 at Milestone 3. Source, requirement and acceptance criteria were populated at M1. The ASR, architecture, data, design, technology, implementation and verification columns were introduced at M2: populated where M2 evidence exists, and carried at a controlled status where it legitimately does not. v0.5 (29/09/2026, R. van der Merwe): data/persistence column completed for all 79 rows; DEC-015 to DEC-017 and CR-001 to CR-004 referenced. Change notes: RTM_v0.5_Change_Notes.md. v0.6 (30/09/2026, C. Burger): ASR / quality-driver link and Architecture / module / component columns completed for all 79 rows from PED §6A (ASR-01 to ASR-06, DEC-014); requirements with no driver are marked explicitly. v0.7 (30/09/2026, R. van der Merwe): Implementation and Verification evidence populated for the 11 requirements the application slice now implements (FR-1.3, FR-1.5, FR-2.2, FR-3.5, FR-6.1 to FR-6.7), after PR #63; FR-1.5, FR-2.2 and FR-3.5 are recorded as partial. Status column unchanged. v0.8 (30/09/2026, E. Lindsay): NFR-3.3 Implementation and Verification evidence added; FR-1.3 and FR-6.7 corrected from Implemented to Partially implemented (AC-FR-1.3 rejected-attempt recording not built; DB-01 layer 3 is M3). Status column unchanged. v0.9 (11/10/2026, E. Lindsay): Implementation and Verification evidence added for FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 after the M3 Phase 0 composition root (PR #83, DEC-018); FR-1.1, FR-1.4 and NFR-1.4 recorded as partial. Design / interface entries for DEC-018 added on the same five rows. The application is reachable over HTTP against the Atlas test cluster (SMOKE-01); no index is evidenced on the cluster. Status column unchanged. Also corrected in v0.9: the NFR-3.4 Data/persistence cell, which said the TTL index enforces idle expiry — DB-01 v0.3 §3.9 states that reading is wrong, and the enforcement is in the application against lastSeenAt (R. van der Merwe's column, corrected by E. Lindsay and notified). The Architecture column on FR-1.4, NFR-1.6 and NFR-3.4 changed from "(planned)" to reflect the composed application (C. Burger's column, corrected by E. Lindsay and notified). NOTE ON EVIDENCE: Implementation and verification evidence is recorded at component level. Each component named is implemented and verified by npm test, with its collaborators substituted (no database, no HTTP). Since v0.9 the composition root (src/composition.js, src/server.js) composes the routes, services, repositories and unit of work, and the session middleware sets req.actor; the application is reachable over HTTP against the Atlas test cluster, recorded in docs/evidence/M3-P0/SMOKE-01_phase0_reachability.txt. SMOKE-01 is reachability evidence only: it does not show that any index exists on the cluster. Where a row cites SMOKE-01, that check ran against the cluster; every other cited test ran without a database. Verification that needs a live database (transaction atomicity and rollback, DB-01 layer 3, audit-trigger lag) is M3. v0.10 (15/10/2026, E. Lindsay): the M3 chain added as four columns (O test cases, P expected result, Q execution evidence, R defect / M3 status), populated for the 27 requirements the M3 release candidate (v3.0-M3-rc) implements or verifies; the other 52 rows are marked "Not in M3 scope" with the reason. Unit evidence is the CI run at the release candidate (Node 22); test evidence records UT-1 to UT-5 and BB-1 to BB-5 (M3_Test_Evidence_Records_v0.1.md); API cases on the test cluster; E2E at v3.0-M3-rc; staging, NFR-2.4 and smoke from the staging deploy record. Defects and debt cited: DEF-011, DEF-019, DEF-020, TD-005, TD-006, TD-008; open items OI-01, OI-15, OI-16, OI-17, OI-18. Columns A to N and the Status summary sheet unchanged. v0.11 (17/10/2026, E. Lindsay): final M4 status for all 79 requirement rows (80 acceptance criteria; FR-2.2 holds AC-FR-2.2a and AC-FR-2.2b in one row, each given its own status) at the frozen build 6408ab7 (PR #136), counted under the strict rule (Met only where the Then clause is shown through the system's own interface): 59 Met, 8 Partially Met, 13 Not Met, 63 of 80 after the RC staging session of 18/10/2026 (at the frozen build before it: 56, 9 and 15, 60.5 of 80). Columns K, L, O, P, Q and R rewritten for every row from the M4 build and its evidence (unit tests, API integration run 3, E2E run 2 in four browsers, NV-101 to NV-173); the cells that depend on the RC on staging were filled from docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md (18/10/2026): NFR-1.3, NFR-2.7 and NFR-3.2 Met; NFR-1.11 and NFR-3.1 Partially Met; NFR-2.1 and NFR-2.4 Not Met (DEF-032, counter contention); NFR-4.1 Not Met (review not performed). CR-001 to CR-004 approved 17/10/2026 by the team, not validated with a client stakeholder: C77, E75, E77, E81, H77, M58, N35, N40, N58, N74, N75, N77, N81 and P75 updated. Defects fixed in the M4 build and cited: DEF-007 to DEF-012 and DEF-022 to DEF-031 (DEF-031: the category name shown as "Request" after a sign-in on the request page). Columns A to J other than C77, E75, E77, E81 and H77 unchanged. The sheet is renamed "RTM v0.11"; the headers of O, Q and R read (M4); the Status summary is updated (A1, B9 to C10, D9, D10).</t>
+  </si>
+  <si>
+    <t>Built: the four role journeys (E2E-1 to E2E-13 on the test cluster), verified on staging at the RC.</t>
+  </si>
+  <si>
+    <t>Verified on staging at v4.0-M4-rc: the four role journeys walked through in a browser (E. Lindsay, 18/10/2026 01:53 to 02:05 UTC).</t>
+  </si>
+  <si>
+    <t>Measured on staging at the RC: submission run and server-side timing from the performance log (perf/submit-run.js, perf/server-timings.js; c858788).</t>
+  </si>
+  <si>
+    <t>Run on staging at v4.0-M4-rc (18/10/2026 01:28 UTC): not met.</t>
+  </si>
+  <si>
+    <t>Implemented: standard-journey load script (perf/load-run.js, c858788), run on staging at the RC.</t>
+  </si>
+  <si>
+    <t>Run on staging at v4.0-M4-rc (18/10/2026 00:59 to 01:11 UTC): failed.</t>
+  </si>
+  <si>
+    <t>Built: passwords are stored as scrypt hashes (DEC-018 §2); inspected on staging at the RC.</t>
+  </si>
+  <si>
+    <t>Implemented: HTTPS on staging with plain HTTP redirected and TLS below 1.2 refused (Nginx, ssl_protocols TLSv1.2 TLSv1.3).</t>
+  </si>
+  <si>
+    <t>Verified on staging at v4.0-M4-rc (T9a, 18/10/2026 02:10 UTC).</t>
+  </si>
+  <si>
+    <t>Built: sessions are stored in MongoDB, not in process memory (DEC-018); verified on staging at the RC.</t>
+  </si>
+  <si>
+    <t>Not verified: the field-to-purpose review was not performed at M4.</t>
+  </si>
+  <si>
+    <t>Staging walkthrough at v4.0-M4-rc: the Requester, Coordinator, Technician and Manager journeys (seed run 8ecb330b).</t>
+  </si>
+  <si>
+    <t>docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, section 10 (18/10/2026 01:53 to 02:05 UTC): every step as expected; request CC-2026-000521 submitted, assigned, resolved and reported.</t>
+  </si>
+  <si>
+    <t>Met (v4.0-M4-rc on staging): all four journeys completed. The server makes no outbound call, so no campus system endpoint is needed.</t>
+  </si>
+  <si>
+    <t>NFR-2.1 submission run (perf/submit-run.js): 100 Requesters submit at the same moment; server-side timings from the performance log.</t>
+  </si>
+  <si>
+    <t>docs/evidence/M4-perf/NFR-2.1_submit_run_2026-10-18.txt; docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, section 8: 27 of 100 confirmed within 60 s, 2 within 3 s server-side; 70 saved, 30 lost.</t>
+  </si>
+  <si>
+    <t>Not Met (v4.0-M4-rc on staging): 2 of 100 confirmations within 3 s server-side (95 required); 30 submissions lost after the transaction retries ran out. DEF-032: counter contention.</t>
+  </si>
+  <si>
+    <t>NFR-2.4 load run (perf/load-run.js): 100 users (50 Coordinators: list, read, reject; 50 Requesters: list, read, submit) for 600 s after a 60 s ramp.</t>
+  </si>
+  <si>
+    <t>docs/evidence/M4-perf/NFR-2.4_load_run_2026-10-18.txt; docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, section 7: 12,130 requests, 17 failed (submissions over the client's 30 s limit, all saved), 0 server errors. M3 run (passed without submission or lists): docs/evidence/M3-perf/NFR-2.4_load_run_2026-10-15.txt.</t>
+  </si>
+  <si>
+    <t>Not Met (v4.0-M4-rc on staging): RESULT FAIL, 17 failed requests (submission timeouts), 0 unhandled server errors. DEF-032: counter contention; RSK-019 indicator reached (about 74 ops/s).</t>
+  </si>
+  <si>
+    <t>npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-147 (docs/evidence/M4-build/); docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, section 11 (T9c, 18/10/2026 02:16 UTC): 243 of 243 stored passwords scrypt, 6 of 6 seed passwords verify, 0 plaintext in the database, the service journal and the Nginx logs.</t>
+  </si>
+  <si>
+    <t>Partially Met (v4.0-M4-rc on staging): the credential store and every log hold only scrypt hashes and no plaintext; the backups clause cannot be shown, because no backups exist (AC-NFR-1.5 Not Met).</t>
+  </si>
+  <si>
+    <t>T9a: a plain HTTP request; OpenSSL s_client at TLS 1.0, 1.1, 1.2 and 1.3 against the staging address.</t>
+  </si>
+  <si>
+    <t>docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, section 11 (T9a): HTTP 301 to HTTPS; TLS 1.0 and 1.1 refused by the server (alert 70); TLS 1.2 and 1.3 with the certificate verified. Re-checked against https://civicconnect.co.za with a Let's Encrypt certificate (18/10/2026 12:30 UTC, section 14): TLS 1.0 and 1.1 refused, TLS 1.2 and 1.3 verified with the name checked.</t>
+  </si>
+  <si>
+    <t>Met (v4.0-M4-rc on staging).</t>
+  </si>
+  <si>
+    <t>npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-140, NV-167 (docs/evidence/M4-build/); docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, section 11 (T9b): 12,114 entries under the NFR-2.4 load, each with exactly operation, durationMs and outcome; 0 personal information; 12,130 operations = 12,114 entries + 16 abandoned.</t>
+  </si>
+  <si>
+    <t>Partially Met (v4.0-M4-rc on staging): format and privacy met under load; the 16 requests abandoned before their response finished have no entry (logged on finish only). DEF-029 (errors logged as "POST /") fixed.</t>
+  </si>
+  <si>
+    <t>npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, section 11 (T9d): the same session accepted by a new process after a service restart (control 401); 8 query plans of the list, search and management views all IXSCAN, 0 COLLSCAN; auditLog never read.</t>
+  </si>
+  <si>
+    <t>Field-to-purpose review against DEC-017 and DB-01 (a document review, not a staging check).</t>
+  </si>
+  <si>
+    <t>None: not performed at M4.</t>
+  </si>
+  <si>
+    <t>Not Met: the field-to-purpose review against DEC-017 was not performed at M4.</t>
+  </si>
+  <si>
+    <t>v0.7 (Robert): 11 rows populated from the application slice after PR #63. v0.8 (Ethan): NFR-3.3 added; FR-1.3 and FR-6.7 corrected to partial. v0.9 (Ethan): FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 added after PR #83. 17 rows populated (8 implemented, 9 partial). Remaining 62: all three members, criterion F, as code is written v0.11 (Ethan): rewritten for all 79 rows from the M4 build at the frozen build 6408ab7 (PR #136); every row has an entry, including the rows not implemented, so 79 populated and 0 outstanding. The rows evidenced on staging were filled from the RC staging record (docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, 18/10/2026).</t>
+  </si>
+  <si>
+    <t>v0.7 (Robert): 11 rows with automated test evidence (npm test 80/80). v0.8 (Ethan): NFR-3.3 added; 12 rows. v0.9 (Ethan): FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 added (npm test 132/132; SMOKE-01 against the Atlas test cluster for reachability); 17 rows. Remaining 62 and live-cluster verification beyond reachability: M3 v0.11 (Ethan): rewritten for all 79 rows with the M4 evidence at 6408ab7: npm test 459 tests (451 pass, 0 fail, 8 skipped), integration 40 of 40 on the test cluster, E2E 56 of 56 in four browsers; 79 populated, 0 outstanding. The rows evidenced on staging were filled from the RC staging record (docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, 18/10/2026).</t>
   </si>
 </sst>
 </file>
@@ -3113,7 +3143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3157,9 +3187,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3494,7 +3521,7 @@
     </row>
     <row r="2" spans="1:18" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -3572,19 +3599,19 @@
         <v>15</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>962</v>
+        <v>941</v>
       </c>
       <c r="P5" s="15" t="s">
         <v>576</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>963</v>
+        <v>942</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="125.4" x14ac:dyDescent="0.3">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -3628,19 +3655,19 @@
         <v>560</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="Q6" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R6" s="16" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -3671,10 +3698,10 @@
       <c r="J7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="20" t="s">
+      <c r="K7" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="L7" s="20" t="s">
+      <c r="L7" s="4" t="s">
         <v>580</v>
       </c>
       <c r="M7" s="7" t="s">
@@ -3684,19 +3711,19 @@
         <v>34</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="Q7" s="16" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="68.400000000000006" x14ac:dyDescent="0.3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
@@ -3740,19 +3767,19 @@
         <v>42</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="Q8" s="16" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="R8" s="16" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="114" x14ac:dyDescent="0.3">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>43</v>
       </c>
@@ -3796,19 +3823,19 @@
         <v>563</v>
       </c>
       <c r="O9" s="16" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="79.8" x14ac:dyDescent="0.3">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>49</v>
       </c>
@@ -3852,19 +3879,19 @@
         <v>56</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="Q10" s="16" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="R10" s="16" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>57</v>
       </c>
@@ -3895,10 +3922,10 @@
       <c r="J11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="L11" s="20" t="s">
+      <c r="L11" s="4" t="s">
         <v>588</v>
       </c>
       <c r="M11" s="7" t="s">
@@ -3908,19 +3935,19 @@
         <v>65</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="Q11" s="16" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="R11" s="16" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="91.2" x14ac:dyDescent="0.3">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
@@ -3964,19 +3991,19 @@
         <v>74</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="P12" s="16" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="Q12" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R12" s="16" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>75</v>
       </c>
@@ -4007,10 +4034,10 @@
       <c r="J13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="L13" s="20" t="s">
+      <c r="L13" s="4" t="s">
         <v>592</v>
       </c>
       <c r="M13" s="7" t="s">
@@ -4020,19 +4047,19 @@
         <v>48</v>
       </c>
       <c r="O13" s="16" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="Q13" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>81</v>
       </c>
@@ -4063,10 +4090,10 @@
       <c r="J14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="20" t="s">
+      <c r="K14" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="L14" s="20" t="s">
+      <c r="L14" s="4" t="s">
         <v>594</v>
       </c>
       <c r="M14" s="7" t="s">
@@ -4076,19 +4103,19 @@
         <v>89</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="Q14" s="16" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R14" s="16" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>90</v>
       </c>
@@ -4119,10 +4146,10 @@
       <c r="J15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="L15" s="20" t="s">
+      <c r="L15" s="4" t="s">
         <v>596</v>
       </c>
       <c r="M15" s="7" t="s">
@@ -4132,19 +4159,19 @@
         <v>48</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="Q15" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R15" s="16" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>97</v>
       </c>
@@ -4175,10 +4202,10 @@
       <c r="J16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="20" t="s">
+      <c r="K16" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="L16" s="20" t="s">
+      <c r="L16" s="4" t="s">
         <v>598</v>
       </c>
       <c r="M16" s="7" t="s">
@@ -4188,19 +4215,19 @@
         <v>103</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="R16" s="16" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>104</v>
       </c>
@@ -4231,10 +4258,10 @@
       <c r="J17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="20" t="s">
+      <c r="K17" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="L17" s="20" t="s">
+      <c r="L17" s="4" t="s">
         <v>600</v>
       </c>
       <c r="M17" s="7" t="s">
@@ -4244,19 +4271,19 @@
         <v>110</v>
       </c>
       <c r="O17" s="16" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="Q17" s="16" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="R17" s="16" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>111</v>
       </c>
@@ -4287,10 +4314,10 @@
       <c r="J18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="20" t="s">
+      <c r="K18" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="L18" s="20" t="s">
+      <c r="L18" s="4" t="s">
         <v>602</v>
       </c>
       <c r="M18" s="7" t="s">
@@ -4300,19 +4327,19 @@
         <v>48</v>
       </c>
       <c r="O18" s="16" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="Q18" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R18" s="16" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>116</v>
       </c>
@@ -4343,10 +4370,10 @@
       <c r="J19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="20" t="s">
+      <c r="K19" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="L19" s="20" t="s">
+      <c r="L19" s="4" t="s">
         <v>604</v>
       </c>
       <c r="M19" s="7" t="s">
@@ -4356,19 +4383,19 @@
         <v>48</v>
       </c>
       <c r="O19" s="16" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="Q19" s="16" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="R19" s="16" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>123</v>
       </c>
@@ -4399,10 +4426,10 @@
       <c r="J20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="L20" s="20" t="s">
+      <c r="L20" s="4" t="s">
         <v>606</v>
       </c>
       <c r="M20" s="7" t="s">
@@ -4412,19 +4439,19 @@
         <v>129</v>
       </c>
       <c r="O20" s="16" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="P20" s="16" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="Q20" s="16" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="R20" s="16" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>130</v>
       </c>
@@ -4468,19 +4495,19 @@
         <v>136</v>
       </c>
       <c r="O21" s="16" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="Q21" s="16" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="R21" s="16" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>137</v>
       </c>
@@ -4511,10 +4538,10 @@
       <c r="J22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="20" t="s">
+      <c r="K22" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="4" t="s">
         <v>610</v>
       </c>
       <c r="M22" s="7" t="s">
@@ -4524,19 +4551,19 @@
         <v>144</v>
       </c>
       <c r="O22" s="16" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="Q22" s="16" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="R22" s="16" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>145</v>
       </c>
@@ -4567,10 +4594,10 @@
       <c r="J23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K23" s="20" t="s">
+      <c r="K23" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="4" t="s">
         <v>612</v>
       </c>
       <c r="M23" s="7" t="s">
@@ -4580,19 +4607,19 @@
         <v>48</v>
       </c>
       <c r="O23" s="16" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="Q23" s="16" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="R23" s="16" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>151</v>
       </c>
@@ -4623,10 +4650,10 @@
       <c r="J24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K24" s="20" t="s">
+      <c r="K24" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="4" t="s">
         <v>614</v>
       </c>
       <c r="M24" s="8" t="s">
@@ -4636,19 +4663,19 @@
         <v>158</v>
       </c>
       <c r="O24" s="16" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="Q24" s="16" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="R24" s="16" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>159</v>
       </c>
@@ -4679,10 +4706,10 @@
       <c r="J25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="20" t="s">
+      <c r="K25" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="4" t="s">
         <v>616</v>
       </c>
       <c r="M25" s="7" t="s">
@@ -4692,19 +4719,19 @@
         <v>26</v>
       </c>
       <c r="O25" s="16" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="P25" s="16" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="Q25" s="16" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="R25" s="16" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>167</v>
       </c>
@@ -4735,10 +4762,10 @@
       <c r="J26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="20" t="s">
+      <c r="K26" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="L26" s="20" t="s">
+      <c r="L26" s="4" t="s">
         <v>618</v>
       </c>
       <c r="M26" s="7" t="s">
@@ -4748,19 +4775,19 @@
         <v>173</v>
       </c>
       <c r="O26" s="16" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="P26" s="16" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="Q26" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="R26" s="16" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>174</v>
       </c>
@@ -4791,10 +4818,10 @@
       <c r="J27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K27" s="20" t="s">
+      <c r="K27" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="L27" s="20" t="s">
+      <c r="L27" s="4" t="s">
         <v>618</v>
       </c>
       <c r="M27" s="7" t="s">
@@ -4804,19 +4831,19 @@
         <v>48</v>
       </c>
       <c r="O27" s="16" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="P27" s="16" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="Q27" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="R27" s="16" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>180</v>
       </c>
@@ -4847,10 +4874,10 @@
       <c r="J28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="L28" s="20" t="s">
+      <c r="L28" s="4" t="s">
         <v>621</v>
       </c>
       <c r="M28" s="7" t="s">
@@ -4860,19 +4887,19 @@
         <v>48</v>
       </c>
       <c r="O28" s="16" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="P28" s="16" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="Q28" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R28" s="16" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="68.400000000000006" x14ac:dyDescent="0.3">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>186</v>
       </c>
@@ -4903,10 +4930,10 @@
       <c r="J29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="20" t="s">
+      <c r="K29" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="L29" s="20" t="s">
+      <c r="L29" s="4" t="s">
         <v>623</v>
       </c>
       <c r="M29" s="7" t="s">
@@ -4916,19 +4943,19 @@
         <v>65</v>
       </c>
       <c r="O29" s="16" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="P29" s="16" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="Q29" s="16" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="R29" s="16" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>193</v>
       </c>
@@ -4959,10 +4986,10 @@
       <c r="J30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="20" t="s">
+      <c r="K30" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="L30" s="20" t="s">
+      <c r="L30" s="4" t="s">
         <v>625</v>
       </c>
       <c r="M30" s="7" t="s">
@@ -4972,19 +4999,19 @@
         <v>103</v>
       </c>
       <c r="O30" s="16" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="P30" s="16" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="Q30" s="16" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="R30" s="16" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>199</v>
       </c>
@@ -5015,10 +5042,10 @@
       <c r="J31" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="20" t="s">
+      <c r="K31" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="L31" s="20" t="s">
+      <c r="L31" s="4" t="s">
         <v>627</v>
       </c>
       <c r="M31" s="7" t="s">
@@ -5028,19 +5055,19 @@
         <v>103</v>
       </c>
       <c r="O31" s="16" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="P31" s="16" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="Q31" s="16" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="R31" s="16" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>206</v>
       </c>
@@ -5071,10 +5098,10 @@
       <c r="J32" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="20" t="s">
+      <c r="K32" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="L32" s="20" t="s">
+      <c r="L32" s="4" t="s">
         <v>629</v>
       </c>
       <c r="M32" s="7" t="s">
@@ -5084,19 +5111,19 @@
         <v>48</v>
       </c>
       <c r="O32" s="16" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="P32" s="16" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="Q32" s="16" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="R32" s="16" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>212</v>
       </c>
@@ -5127,10 +5154,10 @@
       <c r="J33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K33" s="20" t="s">
+      <c r="K33" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="L33" s="20" t="s">
+      <c r="L33" s="4" t="s">
         <v>631</v>
       </c>
       <c r="M33" s="7" t="s">
@@ -5140,19 +5167,19 @@
         <v>48</v>
       </c>
       <c r="O33" s="16" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="P33" s="16" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="Q33" s="16" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="R33" s="16" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>218</v>
       </c>
@@ -5196,16 +5223,16 @@
         <v>224</v>
       </c>
       <c r="O34" s="16" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="P34" s="16" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="Q34" s="16" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="R34" s="16" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="302.39999999999998" x14ac:dyDescent="0.3">
@@ -5249,22 +5276,22 @@
         <v>25</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>970</v>
+        <v>949</v>
       </c>
       <c r="O35" s="16" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="P35" s="16" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="Q35" s="16" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="R35" s="16" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="68.400000000000006" x14ac:dyDescent="0.3">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>232</v>
       </c>
@@ -5308,19 +5335,19 @@
         <v>48</v>
       </c>
       <c r="O36" s="16" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="P36" s="16" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="Q36" s="16" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="R36" s="16" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>236</v>
       </c>
@@ -5364,19 +5391,19 @@
         <v>243</v>
       </c>
       <c r="O37" s="16" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="P37" s="16" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="Q37" s="16" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="R37" s="16" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>244</v>
       </c>
@@ -5420,19 +5447,19 @@
         <v>48</v>
       </c>
       <c r="O38" s="16" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="P38" s="16" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="Q38" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R38" s="16" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>251</v>
       </c>
@@ -5476,16 +5503,16 @@
         <v>257</v>
       </c>
       <c r="O39" s="16" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="P39" s="16" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="Q39" s="16" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="R39" s="16" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="144" x14ac:dyDescent="0.3">
@@ -5529,22 +5556,22 @@
         <v>25</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>971</v>
+        <v>950</v>
       </c>
       <c r="O40" s="16" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="P40" s="16" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="Q40" s="16" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="R40" s="16" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>264</v>
       </c>
@@ -5575,10 +5602,10 @@
       <c r="J41" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="20" t="s">
+      <c r="K41" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="L41" s="20" t="s">
+      <c r="L41" s="4" t="s">
         <v>647</v>
       </c>
       <c r="M41" s="7" t="s">
@@ -5588,19 +5615,19 @@
         <v>26</v>
       </c>
       <c r="O41" s="16" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="P41" s="16" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="Q41" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R41" s="16" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>271</v>
       </c>
@@ -5631,10 +5658,10 @@
       <c r="J42" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K42" s="20" t="s">
+      <c r="K42" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="L42" s="20" t="s">
+      <c r="L42" s="4" t="s">
         <v>649</v>
       </c>
       <c r="M42" s="7" t="s">
@@ -5644,19 +5671,19 @@
         <v>26</v>
       </c>
       <c r="O42" s="16" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="P42" s="16" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="Q42" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R42" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>276</v>
       </c>
@@ -5687,10 +5714,10 @@
       <c r="J43" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K43" s="20" t="s">
+      <c r="K43" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="L43" s="20" t="s">
+      <c r="L43" s="4" t="s">
         <v>651</v>
       </c>
       <c r="M43" s="7" t="s">
@@ -5700,19 +5727,19 @@
         <v>48</v>
       </c>
       <c r="O43" s="16" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="P43" s="16" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="Q43" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="R43" s="16" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>282</v>
       </c>
@@ -5743,10 +5770,10 @@
       <c r="J44" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="20" t="s">
+      <c r="K44" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="L44" s="20" t="s">
+      <c r="L44" s="4" t="s">
         <v>653</v>
       </c>
       <c r="M44" s="7" t="s">
@@ -5756,19 +5783,19 @@
         <v>48</v>
       </c>
       <c r="O44" s="16" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="P44" s="16" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="Q44" s="16" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="R44" s="16" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>288</v>
       </c>
@@ -5799,10 +5826,10 @@
       <c r="J45" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="20" t="s">
+      <c r="K45" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="L45" s="20" t="s">
+      <c r="L45" s="4" t="s">
         <v>655</v>
       </c>
       <c r="M45" s="7" t="s">
@@ -5812,19 +5839,19 @@
         <v>103</v>
       </c>
       <c r="O45" s="16" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="P45" s="16" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="Q45" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R45" s="16" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>293</v>
       </c>
@@ -5855,10 +5882,10 @@
       <c r="J46" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K46" s="20" t="s">
+      <c r="K46" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="L46" s="20" t="s">
+      <c r="L46" s="4" t="s">
         <v>657</v>
       </c>
       <c r="M46" s="7" t="s">
@@ -5868,19 +5895,19 @@
         <v>300</v>
       </c>
       <c r="O46" s="16" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="P46" s="16" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="Q46" s="16" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="R46" s="16" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>301</v>
       </c>
@@ -5911,10 +5938,10 @@
       <c r="J47" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="20" t="s">
+      <c r="K47" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="L47" s="20" t="s">
+      <c r="L47" s="4" t="s">
         <v>659</v>
       </c>
       <c r="M47" s="7" t="s">
@@ -5924,19 +5951,19 @@
         <v>48</v>
       </c>
       <c r="O47" s="16" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="P47" s="16" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="Q47" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R47" s="16" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>305</v>
       </c>
@@ -5967,10 +5994,10 @@
       <c r="J48" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K48" s="20" t="s">
+      <c r="K48" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="L48" s="20" t="s">
+      <c r="L48" s="4" t="s">
         <v>661</v>
       </c>
       <c r="M48" s="7" t="s">
@@ -5980,19 +6007,19 @@
         <v>310</v>
       </c>
       <c r="O48" s="16" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="P48" s="16" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="Q48" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="R48" s="16" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>311</v>
       </c>
@@ -6023,10 +6050,10 @@
       <c r="J49" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K49" s="20" t="s">
+      <c r="K49" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="L49" s="20" t="s">
+      <c r="L49" s="4" t="s">
         <v>663</v>
       </c>
       <c r="M49" s="8" t="s">
@@ -6036,19 +6063,19 @@
         <v>317</v>
       </c>
       <c r="O49" s="16" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="P49" s="16" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="Q49" s="16" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="R49" s="16" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>318</v>
       </c>
@@ -6079,10 +6106,10 @@
       <c r="J50" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K50" s="20" t="s">
+      <c r="K50" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="L50" s="20" t="s">
+      <c r="L50" s="4" t="s">
         <v>659</v>
       </c>
       <c r="M50" s="7" t="s">
@@ -6092,19 +6119,19 @@
         <v>48</v>
       </c>
       <c r="O50" s="16" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="P50" s="16" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="Q50" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="R50" s="16" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>323</v>
       </c>
@@ -6135,10 +6162,10 @@
       <c r="J51" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K51" s="20" t="s">
+      <c r="K51" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="L51" s="20" t="s">
+      <c r="L51" s="4" t="s">
         <v>666</v>
       </c>
       <c r="M51" s="7" t="s">
@@ -6148,19 +6175,19 @@
         <v>329</v>
       </c>
       <c r="O51" s="16" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="P51" s="16" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="Q51" s="16" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="R51" s="16" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>330</v>
       </c>
@@ -6191,10 +6218,10 @@
       <c r="J52" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="20" t="s">
+      <c r="K52" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="L52" s="20" t="s">
+      <c r="L52" s="4" t="s">
         <v>668</v>
       </c>
       <c r="M52" s="8" t="s">
@@ -6204,19 +6231,19 @@
         <v>337</v>
       </c>
       <c r="O52" s="16" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="P52" s="16" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="Q52" s="16" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="R52" s="16" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>338</v>
       </c>
@@ -6247,10 +6274,10 @@
       <c r="J53" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K53" s="20" t="s">
+      <c r="K53" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="L53" s="20" t="s">
+      <c r="L53" s="4" t="s">
         <v>670</v>
       </c>
       <c r="M53" s="7" t="s">
@@ -6260,19 +6287,19 @@
         <v>48</v>
       </c>
       <c r="O53" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P53" s="16" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="Q53" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R53" s="16" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>344</v>
       </c>
@@ -6303,10 +6330,10 @@
       <c r="J54" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K54" s="20" t="s">
+      <c r="K54" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="L54" s="20" t="s">
+      <c r="L54" s="4" t="s">
         <v>672</v>
       </c>
       <c r="M54" s="7" t="s">
@@ -6316,19 +6343,19 @@
         <v>48</v>
       </c>
       <c r="O54" s="16" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="P54" s="16" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="Q54" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="R54" s="16" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>350</v>
       </c>
@@ -6359,10 +6386,10 @@
       <c r="J55" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="K55" s="20" t="s">
+      <c r="K55" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="L55" s="20" t="s">
+      <c r="L55" s="4" t="s">
         <v>674</v>
       </c>
       <c r="M55" s="5" t="s">
@@ -6372,19 +6399,19 @@
         <v>359</v>
       </c>
       <c r="O55" s="16" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="P55" s="16" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="Q55" s="16" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="R55" s="16" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>360</v>
       </c>
@@ -6415,10 +6442,10 @@
       <c r="J56" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K56" s="20" t="s">
+      <c r="K56" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="L56" s="20" t="s">
+      <c r="L56" s="4" t="s">
         <v>676</v>
       </c>
       <c r="M56" s="7" t="s">
@@ -6428,16 +6455,16 @@
         <v>367</v>
       </c>
       <c r="O56" s="16" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="P56" s="16" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="Q56" s="16" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="R56" s="16" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -6471,11 +6498,11 @@
       <c r="J57" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K57" s="20" t="s">
-        <v>677</v>
-      </c>
-      <c r="L57" s="20" t="s">
-        <v>678</v>
+      <c r="K57" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>959</v>
       </c>
       <c r="M57" s="7" t="s">
         <v>25</v>
@@ -6484,19 +6511,19 @@
         <v>48</v>
       </c>
       <c r="O57" s="16" t="s">
-        <v>887</v>
+        <v>969</v>
       </c>
       <c r="P57" s="16" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="Q57" s="16" t="s">
-        <v>889</v>
+        <v>970</v>
       </c>
       <c r="R57" s="16" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>374</v>
       </c>
@@ -6528,28 +6555,28 @@
         <v>24</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>25</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>972</v>
+        <v>951</v>
       </c>
       <c r="O58" s="16" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
       <c r="P58" s="16" t="s">
-        <v>892</v>
+        <v>882</v>
       </c>
       <c r="Q58" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="R58" s="16" t="s">
-        <v>893</v>
+        <v>883</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="57" x14ac:dyDescent="0.3">
@@ -6583,10 +6610,10 @@
       <c r="J59" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="K59" s="20" t="s">
-        <v>681</v>
-      </c>
-      <c r="L59" s="20" t="s">
+      <c r="K59" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>670</v>
       </c>
       <c r="M59" s="5" t="s">
@@ -6596,16 +6623,16 @@
         <v>388</v>
       </c>
       <c r="O59" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P59" s="16" t="s">
-        <v>894</v>
+        <v>884</v>
       </c>
       <c r="Q59" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R59" s="16" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="57" x14ac:dyDescent="0.3">
@@ -6640,10 +6667,10 @@
         <v>394</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M60" s="7" t="s">
         <v>25</v>
@@ -6652,16 +6679,16 @@
         <v>567</v>
       </c>
       <c r="O60" s="16" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="P60" s="16" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="Q60" s="16" t="s">
-        <v>898</v>
+        <v>888</v>
       </c>
       <c r="R60" s="16" t="s">
-        <v>899</v>
+        <v>889</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -6695,11 +6722,11 @@
       <c r="J61" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K61" s="20" t="s">
-        <v>684</v>
-      </c>
-      <c r="L61" s="20" t="s">
-        <v>678</v>
+      <c r="K61" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>961</v>
       </c>
       <c r="M61" s="7" t="s">
         <v>401</v>
@@ -6708,16 +6735,16 @@
         <v>402</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>887</v>
+        <v>972</v>
       </c>
       <c r="P61" s="16" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="Q61" s="16" t="s">
-        <v>889</v>
+        <v>973</v>
       </c>
       <c r="R61" s="16" t="s">
-        <v>901</v>
+        <v>974</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
@@ -6752,7 +6779,7 @@
         <v>24</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="L62" s="6" t="s">
         <v>670</v>
@@ -6764,16 +6791,16 @@
         <v>410</v>
       </c>
       <c r="O62" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P62" s="16" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="Q62" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R62" s="16" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
@@ -6808,7 +6835,7 @@
         <v>24</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="L63" s="6" t="s">
         <v>670</v>
@@ -6820,16 +6847,16 @@
         <v>48</v>
       </c>
       <c r="O63" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P63" s="16" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
       <c r="Q63" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R63" s="16" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -6863,11 +6890,11 @@
       <c r="J64" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K64" s="20" t="s">
-        <v>686</v>
-      </c>
-      <c r="L64" s="20" t="s">
-        <v>678</v>
+      <c r="K64" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>963</v>
       </c>
       <c r="M64" s="7" t="s">
         <v>401</v>
@@ -6876,16 +6903,16 @@
         <v>423</v>
       </c>
       <c r="O64" s="16" t="s">
-        <v>887</v>
+        <v>975</v>
       </c>
       <c r="P64" s="16" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
       <c r="Q64" s="16" t="s">
-        <v>907</v>
+        <v>976</v>
       </c>
       <c r="R64" s="16" t="s">
-        <v>908</v>
+        <v>977</v>
       </c>
     </row>
     <row r="65" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
@@ -6920,7 +6947,7 @@
         <v>24</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="L65" s="6" t="s">
         <v>670</v>
@@ -6932,16 +6959,16 @@
         <v>431</v>
       </c>
       <c r="O65" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P65" s="16" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="Q65" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R65" s="16" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -6975,11 +7002,11 @@
       <c r="J66" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K66" s="20" t="s">
-        <v>687</v>
-      </c>
-      <c r="L66" s="20" t="s">
-        <v>688</v>
+      <c r="K66" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>683</v>
       </c>
       <c r="M66" s="7" t="s">
         <v>25</v>
@@ -6988,16 +7015,16 @@
         <v>48</v>
       </c>
       <c r="O66" s="16" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="P66" s="16" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="Q66" s="16" t="s">
-        <v>913</v>
+        <v>978</v>
       </c>
       <c r="R66" s="16" t="s">
-        <v>914</v>
+        <v>979</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
@@ -7031,11 +7058,11 @@
       <c r="J67" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K67" s="20" t="s">
-        <v>689</v>
-      </c>
-      <c r="L67" s="20" t="s">
-        <v>678</v>
+      <c r="K67" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>966</v>
       </c>
       <c r="M67" s="7" t="s">
         <v>25</v>
@@ -7044,16 +7071,16 @@
         <v>445</v>
       </c>
       <c r="O67" s="16" t="s">
-        <v>887</v>
+        <v>980</v>
       </c>
       <c r="P67" s="16" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="Q67" s="16" t="s">
-        <v>889</v>
+        <v>981</v>
       </c>
       <c r="R67" s="16" t="s">
-        <v>916</v>
+        <v>982</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="175.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7088,10 +7115,10 @@
         <v>24</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="M68" s="7" t="s">
         <v>25</v>
@@ -7100,16 +7127,16 @@
         <v>453</v>
       </c>
       <c r="O68" s="16" t="s">
-        <v>917</v>
+        <v>901</v>
       </c>
       <c r="P68" s="16" t="s">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="Q68" s="16" t="s">
-        <v>919</v>
+        <v>903</v>
       </c>
       <c r="R68" s="16" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -7144,10 +7171,10 @@
         <v>24</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="M69" s="7" t="s">
         <v>25</v>
@@ -7156,16 +7183,16 @@
         <v>563</v>
       </c>
       <c r="O69" s="16" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="P69" s="16" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
       <c r="Q69" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="R69" s="16" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -7199,8 +7226,8 @@
       <c r="J70" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="K70" s="20" t="s">
-        <v>694</v>
+      <c r="K70" s="4" t="s">
+        <v>688</v>
       </c>
       <c r="L70" s="6" t="s">
         <v>670</v>
@@ -7212,16 +7239,16 @@
         <v>445</v>
       </c>
       <c r="O70" s="16" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="P70" s="16" t="s">
-        <v>924</v>
+        <v>908</v>
       </c>
       <c r="Q70" s="16" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="R70" s="16" t="s">
-        <v>925</v>
+        <v>909</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -7255,10 +7282,10 @@
       <c r="J71" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K71" s="20" t="s">
-        <v>695</v>
-      </c>
-      <c r="L71" s="20" t="s">
+      <c r="K71" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="L71" s="4" t="s">
         <v>651</v>
       </c>
       <c r="M71" s="7" t="s">
@@ -7268,16 +7295,16 @@
         <v>110</v>
       </c>
       <c r="O71" s="16" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="P71" s="16" t="s">
-        <v>926</v>
+        <v>910</v>
       </c>
       <c r="Q71" s="16" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="R71" s="16" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -7311,8 +7338,8 @@
       <c r="J72" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K72" s="20" t="s">
-        <v>696</v>
+      <c r="K72" s="4" t="s">
+        <v>690</v>
       </c>
       <c r="L72" s="6" t="s">
         <v>670</v>
@@ -7324,16 +7351,16 @@
         <v>48</v>
       </c>
       <c r="O72" s="16" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="P72" s="16" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
       <c r="Q72" s="16" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="R72" s="16" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -7367,8 +7394,8 @@
       <c r="J73" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="K73" s="20" t="s">
-        <v>697</v>
+      <c r="K73" s="4" t="s">
+        <v>691</v>
       </c>
       <c r="L73" s="6" t="s">
         <v>670</v>
@@ -7380,19 +7407,19 @@
         <v>48</v>
       </c>
       <c r="O73" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P73" s="16" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="Q73" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R73" s="16" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>484</v>
       </c>
@@ -7423,8 +7450,8 @@
       <c r="J74" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="K74" s="20" t="s">
-        <v>698</v>
+      <c r="K74" s="4" t="s">
+        <v>692</v>
       </c>
       <c r="L74" s="6" t="s">
         <v>670</v>
@@ -7433,22 +7460,22 @@
         <v>25</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>973</v>
+        <v>952</v>
       </c>
       <c r="O74" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P74" s="16" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
       <c r="Q74" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R74" s="16" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>491</v>
       </c>
@@ -7462,7 +7489,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>966</v>
+        <v>945</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>94</v>
@@ -7479,29 +7506,29 @@
       <c r="J75" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="K75" s="20" t="s">
-        <v>699</v>
-      </c>
-      <c r="L75" s="20" t="s">
-        <v>700</v>
+      <c r="K75" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>694</v>
       </c>
       <c r="M75" s="7" t="s">
         <v>25</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>974</v>
+        <v>953</v>
       </c>
       <c r="O75" s="16" t="s">
-        <v>934</v>
+        <v>918</v>
       </c>
       <c r="P75" s="16" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
       <c r="Q75" s="16" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
       <c r="R75" s="16" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
@@ -7535,11 +7562,11 @@
       <c r="J76" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K76" s="20" t="s">
-        <v>701</v>
-      </c>
-      <c r="L76" s="20" t="s">
-        <v>702</v>
+      <c r="K76" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>696</v>
       </c>
       <c r="M76" s="7" t="s">
         <v>25</v>
@@ -7548,19 +7575,19 @@
         <v>503</v>
       </c>
       <c r="O76" s="16" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
       <c r="P76" s="16" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="Q76" s="16" t="s">
-        <v>940</v>
+        <v>983</v>
       </c>
       <c r="R76" s="16" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="91.2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>173</v>
       </c>
@@ -7568,13 +7595,13 @@
         <v>504</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>965</v>
+        <v>944</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>967</v>
+        <v>946</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>163</v>
@@ -7583,7 +7610,7 @@
         <v>505</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>969</v>
+        <v>948</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>33</v>
@@ -7591,8 +7618,8 @@
       <c r="J77" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K77" s="20" t="s">
-        <v>703</v>
+      <c r="K77" s="4" t="s">
+        <v>697</v>
       </c>
       <c r="L77" s="6" t="s">
         <v>670</v>
@@ -7601,19 +7628,19 @@
         <v>25</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>975</v>
+        <v>954</v>
       </c>
       <c r="O77" s="16" t="s">
-        <v>942</v>
+        <v>924</v>
       </c>
       <c r="P77" s="16" t="s">
-        <v>943</v>
+        <v>925</v>
       </c>
       <c r="Q77" s="16" t="s">
-        <v>942</v>
+        <v>924</v>
       </c>
       <c r="R77" s="16" t="s">
-        <v>944</v>
+        <v>926</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -7647,11 +7674,11 @@
       <c r="J78" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="K78" s="20" t="s">
-        <v>704</v>
-      </c>
-      <c r="L78" s="20" t="s">
-        <v>693</v>
+      <c r="K78" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>687</v>
       </c>
       <c r="M78" s="7" t="s">
         <v>25</v>
@@ -7660,16 +7687,16 @@
         <v>48</v>
       </c>
       <c r="O78" s="16" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="P78" s="16" t="s">
-        <v>945</v>
+        <v>927</v>
       </c>
       <c r="Q78" s="16" t="s">
-        <v>946</v>
+        <v>985</v>
       </c>
       <c r="R78" s="16" t="s">
-        <v>947</v>
+        <v>982</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
@@ -7704,7 +7731,7 @@
         <v>24</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="L79" s="6" t="s">
         <v>670</v>
@@ -7716,16 +7743,16 @@
         <v>445</v>
       </c>
       <c r="O79" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P79" s="16" t="s">
-        <v>948</v>
+        <v>928</v>
       </c>
       <c r="Q79" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R79" s="16" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
@@ -7759,11 +7786,11 @@
       <c r="J80" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K80" s="20" t="s">
-        <v>706</v>
-      </c>
-      <c r="L80" s="20" t="s">
-        <v>678</v>
+      <c r="K80" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>968</v>
       </c>
       <c r="M80" s="7" t="s">
         <v>25</v>
@@ -7772,16 +7799,16 @@
         <v>525</v>
       </c>
       <c r="O80" s="16" t="s">
-        <v>887</v>
+        <v>986</v>
       </c>
       <c r="P80" s="16" t="s">
-        <v>950</v>
+        <v>930</v>
       </c>
       <c r="Q80" s="16" t="s">
-        <v>889</v>
+        <v>987</v>
       </c>
       <c r="R80" s="16" t="s">
-        <v>951</v>
+        <v>988</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
@@ -7798,7 +7825,7 @@
         <v>19</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>70</v>
@@ -7816,7 +7843,7 @@
         <v>531</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="L81" s="6" t="s">
         <v>670</v>
@@ -7825,22 +7852,22 @@
         <v>532</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>976</v>
+        <v>955</v>
       </c>
       <c r="O81" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P81" s="16" t="s">
-        <v>952</v>
+        <v>931</v>
       </c>
       <c r="Q81" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R81" s="16" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>533</v>
       </c>
@@ -7872,10 +7899,10 @@
         <v>24</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="M82" s="7" t="s">
         <v>25</v>
@@ -7884,19 +7911,19 @@
         <v>48</v>
       </c>
       <c r="O82" s="16" t="s">
-        <v>954</v>
+        <v>933</v>
       </c>
       <c r="P82" s="16" t="s">
-        <v>955</v>
+        <v>934</v>
       </c>
       <c r="Q82" s="16" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="R82" s="16" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>539</v>
       </c>
@@ -7927,11 +7954,11 @@
       <c r="J83" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K83" s="20" t="s">
-        <v>710</v>
-      </c>
-      <c r="L83" s="20" t="s">
-        <v>711</v>
+      <c r="K83" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>704</v>
       </c>
       <c r="M83" s="7" t="s">
         <v>25</v>
@@ -7940,19 +7967,19 @@
         <v>544</v>
       </c>
       <c r="O83" s="16" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="P83" s="16" t="s">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="Q83" s="16" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
       <c r="R83" s="16" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="72" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>545</v>
       </c>
@@ -7984,7 +8011,7 @@
         <v>24</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="L84" s="6" t="s">
         <v>670</v>
@@ -7996,16 +8023,16 @@
         <v>552</v>
       </c>
       <c r="O84" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="P84" s="16" t="s">
-        <v>960</v>
+        <v>939</v>
       </c>
       <c r="Q84" s="16" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R84" s="16" t="s">
-        <v>961</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -8033,7 +8060,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>978</v>
+        <v>956</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -8071,7 +8098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="57" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -8143,7 +8170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="125.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="148.19999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
@@ -8154,14 +8181,14 @@
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="E9" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="125.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="148.19999999999999" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
@@ -8172,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="E10" s="13">
         <f t="shared" si="0"/>
@@ -8430,20 +8457,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c76fba90-bd48-4e65-9fce-772627206c4f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c76fba90-bd48-4e65-9fce-772627206c4f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8466,6 +8493,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B903CEE-E95C-42FD-A969-F1901431EC77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FB2A6B-D58A-4043-A4F7-532B34D9967F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -8480,12 +8515,4 @@
     <ds:schemaRef ds:uri="c76fba90-bd48-4e65-9fce-772627206c4f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B903CEE-E95C-42FD-A969-F1901431EC77}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/Requirements/Requirements Traceability Matrix/Requirements_Traceability_Matrix_v0.11.xlsx
+++ b/docs/Requirements/Requirements Traceability Matrix/Requirements_Traceability_Matrix_v0.11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elind\m4-wt\records\docs\Requirements\Requirements Traceability Matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EBBD59-0368-4C42-ADC6-BA0147F3DEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20D9419-4360-4461-8AC2-E06C86186644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="17472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RTM v0.11" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="998">
   <si>
     <t>Requirements Traceability Matrix</t>
   </si>
@@ -2479,9 +2479,6 @@
     <t>From AC-FR-6.2: the system refuses it and the status is unchanged.</t>
   </si>
   <si>
-    <t>E2E run 2 at 6408ab7, 56 of 56 in Chromium 156, Chrome 155, Edge 155 and Firefox 157 (Playwright's build), retries 0 (docs/evidence/M4-build/E2E_run_2026-10-17_final_four_browsers_run2.txt); API integration run 3 at 6408ab7, 40 of 40 on the test cluster (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt); npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-153 (docs/evidence/M4-build/).</t>
-  </si>
-  <si>
     <t>Met (frozen build 6408ab7). E2E-4 (refusals); the edges and roles are a team proposal (OI-15).</t>
   </si>
   <si>
@@ -2491,9 +2488,6 @@
     <t>From AC-FR-6.3: the entry records the acting user, the previous status, the new status, the date and the time.</t>
   </si>
   <si>
-    <t>E2E run 2 at 6408ab7, 56 of 56 in Chromium 156, Chrome 155, Edge 155 and Firefox 157 (Playwright's build), retries 0 (docs/evidence/M4-build/E2E_run_2026-10-17_final_four_browsers_run2.txt); API integration run 3 at 6408ab7, 40 of 40 on the test cluster (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt); npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-102, NV-158 (docs/evidence/M4-build/).</t>
-  </si>
-  <si>
     <t>Met (frozen build 6408ab7). DEF-007 completed by e973a9d (replay body).</t>
   </si>
   <si>
@@ -2503,9 +2497,6 @@
     <t>From AC-FR-6.4: the system refuses it and the status is unchanged.</t>
   </si>
   <si>
-    <t>E2E run 2 at 6408ab7, 56 of 56 in Chromium 156, Chrome 155, Edge 155 and Firefox 157 (Playwright's build), retries 0 (docs/evidence/M4-build/E2E_run_2026-10-17_final_four_browsers_run2.txt); API integration run 3 at 6408ab7, 40 of 40 on the test cluster (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt); npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-134 (docs/evidence/M4-build/).</t>
-  </si>
-  <si>
     <t>Met (frozen build 6408ab7). DEF-011 (a wrong role answered 422) fixed.</t>
   </si>
   <si>
@@ -2785,9 +2776,6 @@
     <t>From AC-NFR-1.8: each holds a separate schema, no environment reads another's data, and every schema change is traceable to a migration script rather than a manual alteration.</t>
   </si>
   <si>
-    <t>Partially Met (frozen build 6408ab7): development and production are not shown (no production host, OI-21).</t>
-  </si>
-  <si>
     <t>From AC-NFR-1.9: a trigger-written audit row exists for that modification, and the migration script that created the trigger is present and ordered in the repository.</t>
   </si>
   <si>
@@ -2800,9 +2788,6 @@
     <t>From AC-NFR-1.10 v0.3 (CR-001, approved 17/10/2026): a failure injected after the first write and before commit changes neither document and publishes no event. The two auditLog clauses are not tested: the Atlas trigger is not deployed</t>
   </si>
   <si>
-    <t>API integration run 3 at 6408ab7, 40 of 40 on the test cluster (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt); npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-102, NV-121 (docs/evidence/M4-build/).</t>
-  </si>
-  <si>
     <t>Partially Met (frozen build 6408ab7) against AC-NFR-1.10 v0.3 (CR-001, approved 17/10/2026): neither document changes and no event is published; the two auditLog clauses are not shown (trigger not deployed).</t>
   </si>
   <si>
@@ -2911,9 +2896,6 @@
     <t>Column completeness at v0.11</t>
   </si>
   <si>
-    <t>Live artefact, version 0.9 at Milestone 3. Source, requirement and acceptance criteria were populated at M1. The ASR, architecture, data, design, technology, implementation and verification columns were introduced at M2: populated where M2 evidence exists, and carried at a controlled status where it legitimately does not. v0.5 (29/09/2026, R. van der Merwe): data/persistence column completed for all 79 rows; DEC-015 to DEC-017 and CR-001 to CR-004 referenced. Change notes: RTM_v0.5_Change_Notes.md. v0.6 (30/09/2026, C. Burger): ASR / quality-driver link and Architecture / module / component columns completed for all 79 rows from PED §6A (ASR-01 to ASR-06, DEC-014); requirements with no driver are marked explicitly. v0.7 (30/09/2026, R. van der Merwe): Implementation and Verification evidence populated for the 11 requirements the application slice now implements (FR-1.3, FR-1.5, FR-2.2, FR-3.5, FR-6.1 to FR-6.7), after PR #63; FR-1.5, FR-2.2 and FR-3.5 are recorded as partial. Status column unchanged. v0.8 (30/09/2026, E. Lindsay): NFR-3.3 Implementation and Verification evidence added; FR-1.3 and FR-6.7 corrected from Implemented to Partially implemented (AC-FR-1.3 rejected-attempt recording not built; DB-01 layer 3 is M3). Status column unchanged. v0.9 (11/10/2026, E. Lindsay): Implementation and Verification evidence added for FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 after the M3 Phase 0 composition root (PR #83, DEC-018); FR-1.1, FR-1.4 and NFR-1.4 recorded as partial. Design / interface entries for DEC-018 added on the same five rows. The application is reachable over HTTP against the Atlas test cluster (SMOKE-01); no index is evidenced on the cluster. Status column unchanged. Also corrected in v0.9: the NFR-3.4 Data/persistence cell, which said the TTL index enforces idle expiry — DB-01 v0.3 §3.9 states that reading is wrong, and the enforcement is in the application against lastSeenAt (R. van der Merwe's column, corrected by E. Lindsay and notified). The Architecture column on FR-1.4, NFR-1.6 and NFR-3.4 changed from "(planned)" to reflect the composed application (C. Burger's column, corrected by E. Lindsay and notified). NOTE ON EVIDENCE: Implementation and verification evidence is recorded at component level. Each component named is implemented and verified by npm test, with its collaborators substituted (no database, no HTTP). Since v0.9 the composition root (src/composition.js, src/server.js) composes the routes, services, repositories and unit of work, and the session middleware sets req.actor; the application is reachable over HTTP against the Atlas test cluster, recorded in docs/evidence/M3-P0/SMOKE-01_phase0_reachability.txt. SMOKE-01 is reachability evidence only: it does not show that any index exists on the cluster. Where a row cites SMOKE-01, that check ran against the cluster; every other cited test ran without a database. Verification that needs a live database (transaction atomicity and rollback, DB-01 layer 3, audit-trigger lag) is M3. v0.10 (15/10/2026, E. Lindsay): the M3 chain added as four columns (O test cases, P expected result, Q execution evidence, R defect / M3 status), populated for the 27 requirements the M3 release candidate (v3.0-M3-rc) implements or verifies; the other 52 rows are marked "Not in M3 scope" with the reason. Unit evidence is the CI run at the release candidate (Node 22); test evidence records UT-1 to UT-5 and BB-1 to BB-5 (M3_Test_Evidence_Records_v0.1.md); API cases on the test cluster; E2E at v3.0-M3-rc; staging, NFR-2.4 and smoke from the staging deploy record. Defects and debt cited: DEF-011, DEF-019, DEF-020, TD-005, TD-006, TD-008; open items OI-01, OI-15, OI-16, OI-17, OI-18. Columns A to N and the Status summary sheet unchanged. v0.11 (17/10/2026, E. Lindsay): final M4 status for all 79 requirement rows (80 acceptance criteria; FR-2.2 holds AC-FR-2.2a and AC-FR-2.2b in one row, each given its own status) at the frozen build 6408ab7 (PR #136), counted under the strict rule (Met only where the Then clause is shown through the system's own interface): 59 Met, 8 Partially Met, 13 Not Met, 63 of 80 after the RC staging session of 18/10/2026 (at the frozen build before it: 56, 9 and 15, 60.5 of 80). Columns K, L, O, P, Q and R rewritten for every row from the M4 build and its evidence (unit tests, API integration run 3, E2E run 2 in four browsers, NV-101 to NV-173); the cells that depend on the RC on staging were filled from docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md (18/10/2026): NFR-1.3, NFR-2.7 and NFR-3.2 Met; NFR-1.11 and NFR-3.1 Partially Met; NFR-2.1 and NFR-2.4 Not Met (DEF-032, counter contention); NFR-4.1 Not Met (review not performed). CR-001 to CR-004 approved 17/10/2026 by the team, not validated with a client stakeholder: C77, E75, E77, E81, H77, M58, N35, N40, N58, N74, N75, N77, N81 and P75 updated. Defects fixed in the M4 build and cited: DEF-007 to DEF-012 and DEF-022 to DEF-031 (DEF-031: the category name shown as "Request" after a sign-in on the request page). Columns A to J other than C77, E75, E77, E81 and H77 unchanged. The sheet is renamed "RTM v0.11"; the headers of O, Q and R read (M4); the Status summary is updated (A1, B9 to C10, D9, D10).</t>
-  </si>
-  <si>
     <t>Built: the four role journeys (E2E-1 to E2E-13 on the test cluster), verified on staging at the RC.</t>
   </si>
   <si>
@@ -3011,6 +2993,45 @@
   </si>
   <si>
     <t>v0.7 (Robert): 11 rows with automated test evidence (npm test 80/80). v0.8 (Ethan): NFR-3.3 added; 12 rows. v0.9 (Ethan): FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 added (npm test 132/132; SMOKE-01 against the Atlas test cluster for reachability); 17 rows. Remaining 62 and live-cluster verification beyond reachability: M3 v0.11 (Ethan): rewritten for all 79 rows with the M4 evidence at 6408ab7: npm test 459 tests (451 pass, 0 fail, 8 skipped), integration 40 of 40 on the test cluster, E2E 56 of 56 in four browsers; 79 populated, 0 outstanding. The rows evidenced on staging were filled from the RC staging record (docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, 18/10/2026).</t>
+  </si>
+  <si>
+    <t>Live artefact, version 0.9 at Milestone 3. Source, requirement and acceptance criteria were populated at M1. The ASR, architecture, data, design, technology, implementation and verification columns were introduced at M2: populated where M2 evidence exists, and carried at a controlled status where it legitimately does not. v0.5 (29/09/2026, R. van der Merwe): data/persistence column completed for all 79 rows; DEC-015 to DEC-017 and CR-001 to CR-004 referenced. Change notes: RTM_v0.5_Change_Notes.md. v0.6 (30/09/2026, C. Burger): ASR / quality-driver link and Architecture / module / component columns completed for all 79 rows from PED §6A (ASR-01 to ASR-06, DEC-014); requirements with no driver are marked explicitly. v0.7 (30/09/2026, R. van der Merwe): Implementation and Verification evidence populated for the 11 requirements the application slice now implements (FR-1.3, FR-1.5, FR-2.2, FR-3.5, FR-6.1 to FR-6.7), after PR #63; FR-1.5, FR-2.2 and FR-3.5 are recorded as partial. Status column unchanged. v0.8 (30/09/2026, E. Lindsay): NFR-3.3 Implementation and Verification evidence added; FR-1.3 and FR-6.7 corrected from Implemented to Partially implemented (AC-FR-1.3 rejected-attempt recording not built; DB-01 layer 3 is M3). Status column unchanged. v0.9 (11/10/2026, E. Lindsay): Implementation and Verification evidence added for FR-1.1, FR-1.4, NFR-1.4, NFR-1.6 and NFR-3.4 after the M3 Phase 0 composition root (PR #83, DEC-018); FR-1.1, FR-1.4 and NFR-1.4 recorded as partial. Design / interface entries for DEC-018 added on the same five rows. The application is reachable over HTTP against the Atlas test cluster (SMOKE-01); no index is evidenced on the cluster. Status column unchanged. Also corrected in v0.9: the NFR-3.4 Data/persistence cell, which said the TTL index enforces idle expiry — DB-01 v0.3 §3.9 states that reading is wrong, and the enforcement is in the application against lastSeenAt (R. van der Merwe's column, corrected by E. Lindsay and notified). The Architecture column on FR-1.4, NFR-1.6 and NFR-3.4 changed from "(planned)" to reflect the composed application (C. Burger's column, corrected by E. Lindsay and notified). NOTE ON EVIDENCE: Implementation and verification evidence is recorded at component level. Each component named is implemented and verified by npm test, with its collaborators substituted (no database, no HTTP). Since v0.9 the composition root (src/composition.js, src/server.js) composes the routes, services, repositories and unit of work, and the session middleware sets req.actor; the application is reachable over HTTP against the Atlas test cluster, recorded in docs/evidence/M3-P0/SMOKE-01_phase0_reachability.txt. SMOKE-01 is reachability evidence only: it does not show that any index exists on the cluster. Where a row cites SMOKE-01, that check ran against the cluster; every other cited test ran without a database. Verification that needs a live database (transaction atomicity and rollback, DB-01 layer 3, audit-trigger lag) is M3. v0.10 (15/10/2026, E. Lindsay): the M3 chain added as four columns (O test cases, P expected result, Q execution evidence, R defect / M3 status), populated for the 27 requirements the M3 release candidate (v3.0-M3-rc) implements or verifies; the other 52 rows are marked "Not in M3 scope" with the reason. Unit evidence is the CI run at the release candidate (Node 22); test evidence records UT-1 to UT-5 and BB-1 to BB-5 (M3_Test_Evidence_Records_v0.1.md); API cases on the test cluster; E2E at v3.0-M3-rc; staging, NFR-2.4 and smoke from the staging deploy record. Defects and debt cited: DEF-011, DEF-019, DEF-020, TD-005, TD-006, TD-008; open items OI-01, OI-15, OI-16, OI-17, OI-18. Columns A to N and the Status summary sheet unchanged. v0.11 (17/10/2026, E. Lindsay): final M4 status for all 79 requirement rows (80 acceptance criteria; FR-2.2 holds AC-FR-2.2a and AC-FR-2.2b in one row, each given its own status) at the frozen build 6408ab7 (PR #136), counted under the strict rule (Met only where the Then clause is shown through the system's own interface): 59 Met, 8 Partially Met, 13 Not Met, 63 of 80 after the RC staging session of 18/10/2026 (at the frozen build before it: 56, 9 and 15, 60.5 of 80). Columns K, L, O, P, Q and R rewritten for every row from the M4 build and its evidence (unit tests, API integration run 3, E2E run 2 in four browsers, NV-101 to NV-173); the cells that depend on the RC on staging were filled from docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md (18/10/2026): NFR-1.3, NFR-2.7 and NFR-3.2 Met; NFR-1.11 and NFR-3.1 Partially Met; NFR-2.1 and NFR-2.4 Not Met (DEF-032, counter contention); NFR-4.1 Not Met (review not performed). CR-001 to CR-004 approved 17/10/2026 by the team, not validated with a client stakeholder: C77, E75, E77, E81, H77, M58, N35, N40, N58, N74, N75, N77, N81 and P75 updated. Defects fixed in the M4 build and cited: DEF-007 to DEF-012 and DEF-022 to DEF-031 (DEF-031: the category name shown as "Request" after a sign-in on the request page). Columns A to J other than C77, E75, E77, E81 and H77 unchanged. The sheet is renamed "RTM v0.11"; the headers of O, Q and R read (M4); the Status summary is updated (A1, B9 to C10, D9, D10). Third pass (18/10/2026, from C. Burger's review): L70 and L72 (NFR-3.5, NFR-1.7) cite the CI gate demonstrations GATE-01 and GATE-02 in place of "Not verified", and Q70 and Q72 add them; Q35 to Q37 and Q75 (FR-6.2 to FR-6.4, NFR-1.10) add the integration cases in CI (run 39079571516); L73, O73, Q73 and R73 (NFR-1.8, still Partially Met) cite the index provisioning runs on the test and staging clusters and NV-87, and record that the staging counters collection was created by hand.</t>
+  </si>
+  <si>
+    <t>Verified in CI: the full-history secret scan (Gitleaks on HEAD --full-history, and on the text of Office documents) is a required check on every PR to dev and main. Seen to fail: GATE-01 (CI run 38357191208) reported six generic-api-key findings and blocked the merge (file hashes, not credentials); GATE-02 (CI run 38437891644) showed the Office-document extraction fails closed.</t>
+  </si>
+  <si>
+    <t>Verified in CI: the layer check is a step of the required Build and test job on every PR to dev and main. GATE-01 (C. Burger, 13/10/2026, PR #90, CI run 38357191208): a route file re-exporting a model failed the layer check and the merge was blocked. GATE-02 (CI run 38437891644): the check fails closed when src/routes or src/middleware is missing. It covers src/routes and src/middleware only (R).</t>
+  </si>
+  <si>
+    <t>Verified for the test and staging environments only: each cluster was inspected separately and brought to its declared indexes by the provisioning script. Development and production were not inspected (no production host).</t>
+  </si>
+  <si>
+    <t>Index provisioning (scripts/atlas) run against the test cluster and the staging cluster, each listing the schema it found; the host guard that refuses a URI for the wrong cluster (NV-87).</t>
+  </si>
+  <si>
+    <t>E2E run 2 at 6408ab7, 56 of 56 in Chromium 156, Chrome 155, Edge 155 and Firefox 157 (Playwright's build), retries 0 (docs/evidence/M4-build/E2E_run_2026-10-17_final_four_browsers_run2.txt); API integration run 3 at 6408ab7, 40 of 40 on the test cluster (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt); npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-153 (docs/evidence/M4-build/). The integration cases run in CI on every PR to dev and main (a required check since 18/10/2026; TD-008), against a MongoDB 8.0 single-node replica set: 40 of 40, 0 skipped, on the dev push run 39079571516 (cb8bca3, 17/10/2026 23:35 UTC).</t>
+  </si>
+  <si>
+    <t>E2E run 2 at 6408ab7, 56 of 56 in Chromium 156, Chrome 155, Edge 155 and Firefox 157 (Playwright's build), retries 0 (docs/evidence/M4-build/E2E_run_2026-10-17_final_four_browsers_run2.txt); API integration run 3 at 6408ab7, 40 of 40 on the test cluster (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt); npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-102, NV-158 (docs/evidence/M4-build/). The integration cases run in CI on every PR to dev and main (a required check since 18/10/2026; TD-008), against a MongoDB 8.0 single-node replica set: 40 of 40, 0 skipped, on the dev push run 39079571516 (cb8bca3, 17/10/2026 23:35 UTC).</t>
+  </si>
+  <si>
+    <t>E2E run 2 at 6408ab7, 56 of 56 in Chromium 156, Chrome 155, Edge 155 and Firefox 157 (Playwright's build), retries 0 (docs/evidence/M4-build/E2E_run_2026-10-17_final_four_browsers_run2.txt); API integration run 3 at 6408ab7, 40 of 40 on the test cluster (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt); npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-134 (docs/evidence/M4-build/). The integration cases run in CI on every PR to dev and main (a required check since 18/10/2026; TD-008), against a MongoDB 8.0 single-node replica set: 40 of 40, 0 skipped, on the dev push run 39079571516 (cb8bca3, 17/10/2026 23:35 UTC).</t>
+  </si>
+  <si>
+    <t>secret scan green on PR #136 (CI run 39061540226); seen to fail: docs/evidence/M3-CI/GATE-01_layer_boundary_demonstration.txt and GATE-01_4_secret_scan_log.png (CI run 38357191208), docs/evidence/M3-CI/GATE-02_fail_closed_demonstration.txt (CI run 38437891644).</t>
+  </si>
+  <si>
+    <t>CI run 39061540226 (Build and test job, layer check step); seen to fail: docs/evidence/M3-CI/GATE-01_layer_boundary_demonstration.txt and GATE-01_3_layer_check_log.png (CI run 38357191208), docs/evidence/M3-CI/GATE-02_fail_closed_demonstration.txt (CI run 38437891644).</t>
+  </si>
+  <si>
+    <t>docs/evidence/M3-indexes/index_provisioning_test_run2.txt (test, 14/10/2026) and docs/evidence/M3-indexes/index_provisioning_staging_run2.txt (staging, 15/10/2026): RESULT PASS, 21 of 21 declared indexes over 10 collections on each; docs/evidence/M3-indexes/NV-87_host_guard_on_whole_URI.txt (seen to fail). docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md, section 3: the staging counters collection was created by hand on 17/10/2026.</t>
+  </si>
+  <si>
+    <t>API integration run 3 at 6408ab7, 40 of 40 on the test cluster (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt); npm test at the frozen build 6408ab7: 459 tests, 451 pass, 0 fail, 8 skipped (the integration cases, which skip without a database); CI run 39061540226 on PR #136 (45c6b06) green; NV-102, NV-121 (docs/evidence/M4-build/). The integration cases run in CI on every PR to dev and main (a required check since 18/10/2026; TD-008), against a MongoDB 8.0 single-node replica set: 40 of 40, 0 skipped, on the dev push run 39079571516 (cb8bca3, 17/10/2026 23:35 UTC).</t>
+  </si>
+  <si>
+    <t>Partially Met (frozen build 6408ab7): test and staging hold separate schemas, each inspected and provisioned by script; development and production are not shown (no production host, OI-21). The migration clause is not met in full: the counters collection on staging was created by hand (17/10/2026), not by a script.</t>
   </si>
 </sst>
 </file>
@@ -3521,7 +3542,7 @@
     </row>
     <row r="2" spans="1:18" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>957</v>
+        <v>985</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -3599,16 +3620,16 @@
         <v>15</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="P5" s="15" t="s">
         <v>576</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
@@ -5235,7 +5256,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>225</v>
       </c>
@@ -5276,7 +5297,7 @@
         <v>25</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="O35" s="16" t="s">
         <v>811</v>
@@ -5285,13 +5306,13 @@
         <v>812</v>
       </c>
       <c r="Q35" s="16" t="s">
+        <v>990</v>
+      </c>
+      <c r="R35" s="16" t="s">
         <v>813</v>
       </c>
-      <c r="R35" s="16" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:18" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>232</v>
       </c>
@@ -5335,19 +5356,19 @@
         <v>48</v>
       </c>
       <c r="O36" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="P36" s="16" t="s">
         <v>815</v>
       </c>
-      <c r="P36" s="16" t="s">
+      <c r="Q36" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="R36" s="16" t="s">
         <v>816</v>
       </c>
-      <c r="Q36" s="16" t="s">
-        <v>817</v>
-      </c>
-      <c r="R36" s="16" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:18" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>236</v>
       </c>
@@ -5391,16 +5412,16 @@
         <v>243</v>
       </c>
       <c r="O37" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="P37" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="Q37" s="16" t="s">
+        <v>992</v>
+      </c>
+      <c r="R37" s="16" t="s">
         <v>819</v>
-      </c>
-      <c r="P37" s="16" t="s">
-        <v>820</v>
-      </c>
-      <c r="Q37" s="16" t="s">
-        <v>821</v>
-      </c>
-      <c r="R37" s="16" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
@@ -5447,16 +5468,16 @@
         <v>48</v>
       </c>
       <c r="O38" s="16" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="P38" s="16" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="Q38" s="16" t="s">
         <v>708</v>
       </c>
       <c r="R38" s="16" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="216" x14ac:dyDescent="0.3">
@@ -5503,16 +5524,16 @@
         <v>257</v>
       </c>
       <c r="O39" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="P39" s="16" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q39" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="R39" s="16" t="s">
         <v>826</v>
-      </c>
-      <c r="P39" s="16" t="s">
-        <v>827</v>
-      </c>
-      <c r="Q39" s="16" t="s">
-        <v>828</v>
-      </c>
-      <c r="R39" s="16" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="144" x14ac:dyDescent="0.3">
@@ -5556,19 +5577,19 @@
         <v>25</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="O40" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="P40" s="16" t="s">
+        <v>828</v>
+      </c>
+      <c r="Q40" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="R40" s="16" t="s">
         <v>830</v>
-      </c>
-      <c r="P40" s="16" t="s">
-        <v>831</v>
-      </c>
-      <c r="Q40" s="16" t="s">
-        <v>832</v>
-      </c>
-      <c r="R40" s="16" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
@@ -5615,16 +5636,16 @@
         <v>26</v>
       </c>
       <c r="O41" s="16" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="P41" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="Q41" s="16" t="s">
         <v>708</v>
       </c>
       <c r="R41" s="16" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
@@ -5671,16 +5692,16 @@
         <v>26</v>
       </c>
       <c r="O42" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="P42" s="16" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="Q42" s="16" t="s">
         <v>708</v>
       </c>
       <c r="R42" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
@@ -5727,10 +5748,10 @@
         <v>48</v>
       </c>
       <c r="O43" s="16" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="P43" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="Q43" s="16" t="s">
         <v>783</v>
@@ -5783,13 +5804,13 @@
         <v>48</v>
       </c>
       <c r="O44" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="P44" s="16" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q44" s="16" t="s">
         <v>840</v>
-      </c>
-      <c r="P44" s="16" t="s">
-        <v>842</v>
-      </c>
-      <c r="Q44" s="16" t="s">
-        <v>843</v>
       </c>
       <c r="R44" s="16" t="s">
         <v>784</v>
@@ -5839,16 +5860,16 @@
         <v>103</v>
       </c>
       <c r="O45" s="16" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="P45" s="16" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="Q45" s="16" t="s">
         <v>708</v>
       </c>
       <c r="R45" s="16" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="216" x14ac:dyDescent="0.3">
@@ -5895,16 +5916,16 @@
         <v>300</v>
       </c>
       <c r="O46" s="16" t="s">
+        <v>844</v>
+      </c>
+      <c r="P46" s="16" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q46" s="16" t="s">
+        <v>846</v>
+      </c>
+      <c r="R46" s="16" t="s">
         <v>847</v>
-      </c>
-      <c r="P46" s="16" t="s">
-        <v>848</v>
-      </c>
-      <c r="Q46" s="16" t="s">
-        <v>849</v>
-      </c>
-      <c r="R46" s="16" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
@@ -5951,16 +5972,16 @@
         <v>48</v>
       </c>
       <c r="O47" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="P47" s="16" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="Q47" s="16" t="s">
         <v>708</v>
       </c>
       <c r="R47" s="16" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
@@ -6007,10 +6028,10 @@
         <v>310</v>
       </c>
       <c r="O48" s="16" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="P48" s="16" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="Q48" s="16" t="s">
         <v>783</v>
@@ -6063,16 +6084,16 @@
         <v>317</v>
       </c>
       <c r="O49" s="16" t="s">
+        <v>852</v>
+      </c>
+      <c r="P49" s="16" t="s">
+        <v>853</v>
+      </c>
+      <c r="Q49" s="16" t="s">
+        <v>854</v>
+      </c>
+      <c r="R49" s="16" t="s">
         <v>855</v>
-      </c>
-      <c r="P49" s="16" t="s">
-        <v>856</v>
-      </c>
-      <c r="Q49" s="16" t="s">
-        <v>857</v>
-      </c>
-      <c r="R49" s="16" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
@@ -6119,16 +6140,16 @@
         <v>48</v>
       </c>
       <c r="O50" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="P50" s="16" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="Q50" s="16" t="s">
         <v>708</v>
       </c>
       <c r="R50" s="16" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
@@ -6175,13 +6196,13 @@
         <v>329</v>
       </c>
       <c r="O51" s="16" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="P51" s="16" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="Q51" s="16" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="R51" s="16" t="s">
         <v>768</v>
@@ -6231,16 +6252,16 @@
         <v>337</v>
       </c>
       <c r="O52" s="16" t="s">
+        <v>860</v>
+      </c>
+      <c r="P52" s="16" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q52" s="16" t="s">
+        <v>862</v>
+      </c>
+      <c r="R52" s="16" t="s">
         <v>863</v>
-      </c>
-      <c r="P52" s="16" t="s">
-        <v>864</v>
-      </c>
-      <c r="Q52" s="16" t="s">
-        <v>865</v>
-      </c>
-      <c r="R52" s="16" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
@@ -6287,16 +6308,16 @@
         <v>48</v>
       </c>
       <c r="O53" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P53" s="16" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="Q53" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R53" s="16" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
@@ -6343,10 +6364,10 @@
         <v>48</v>
       </c>
       <c r="O54" s="16" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="P54" s="16" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="Q54" s="16" t="s">
         <v>783</v>
@@ -6399,16 +6420,16 @@
         <v>359</v>
       </c>
       <c r="O55" s="16" t="s">
+        <v>869</v>
+      </c>
+      <c r="P55" s="16" t="s">
+        <v>870</v>
+      </c>
+      <c r="Q55" s="16" t="s">
+        <v>871</v>
+      </c>
+      <c r="R55" s="16" t="s">
         <v>872</v>
-      </c>
-      <c r="P55" s="16" t="s">
-        <v>873</v>
-      </c>
-      <c r="Q55" s="16" t="s">
-        <v>874</v>
-      </c>
-      <c r="R55" s="16" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
@@ -6455,19 +6476,19 @@
         <v>367</v>
       </c>
       <c r="O56" s="16" t="s">
+        <v>873</v>
+      </c>
+      <c r="P56" s="16" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q56" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="R56" s="16" t="s">
         <v>876</v>
       </c>
-      <c r="P56" s="16" t="s">
-        <v>877</v>
-      </c>
-      <c r="Q56" s="16" t="s">
-        <v>878</v>
-      </c>
-      <c r="R56" s="16" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>368</v>
       </c>
@@ -6499,10 +6520,10 @@
         <v>24</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="M57" s="7" t="s">
         <v>25</v>
@@ -6511,19 +6532,19 @@
         <v>48</v>
       </c>
       <c r="O57" s="16" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="P57" s="16" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="Q57" s="16" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="R57" s="16" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" ht="79.8" x14ac:dyDescent="0.3">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>374</v>
       </c>
@@ -6564,22 +6585,22 @@
         <v>25</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="O58" s="16" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P58" s="16" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="Q58" s="16" t="s">
         <v>783</v>
       </c>
       <c r="R58" s="16" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>380</v>
       </c>
@@ -6623,19 +6644,19 @@
         <v>388</v>
       </c>
       <c r="O59" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P59" s="16" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="Q59" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R59" s="16" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" ht="57" x14ac:dyDescent="0.3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>389</v>
       </c>
@@ -6679,19 +6700,19 @@
         <v>567</v>
       </c>
       <c r="O60" s="16" t="s">
+        <v>883</v>
+      </c>
+      <c r="P60" s="16" t="s">
+        <v>884</v>
+      </c>
+      <c r="Q60" s="16" t="s">
+        <v>885</v>
+      </c>
+      <c r="R60" s="16" t="s">
         <v>886</v>
       </c>
-      <c r="P60" s="16" t="s">
-        <v>887</v>
-      </c>
-      <c r="Q60" s="16" t="s">
-        <v>888</v>
-      </c>
-      <c r="R60" s="16" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>395</v>
       </c>
@@ -6723,10 +6744,10 @@
         <v>24</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="M61" s="7" t="s">
         <v>401</v>
@@ -6735,19 +6756,19 @@
         <v>402</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="P61" s="16" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="Q61" s="16" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="R61" s="16" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>403</v>
       </c>
@@ -6791,19 +6812,19 @@
         <v>410</v>
       </c>
       <c r="O62" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P62" s="16" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="Q62" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R62" s="16" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>411</v>
       </c>
@@ -6847,19 +6868,19 @@
         <v>48</v>
       </c>
       <c r="O63" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P63" s="16" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="Q63" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R63" s="16" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>417</v>
       </c>
@@ -6891,10 +6912,10 @@
         <v>24</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="M64" s="7" t="s">
         <v>401</v>
@@ -6903,19 +6924,19 @@
         <v>423</v>
       </c>
       <c r="O64" s="16" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="P64" s="16" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="Q64" s="16" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="R64" s="16" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>424</v>
       </c>
@@ -6959,19 +6980,19 @@
         <v>431</v>
       </c>
       <c r="O65" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P65" s="16" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="Q65" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R65" s="16" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>432</v>
       </c>
@@ -7003,7 +7024,7 @@
         <v>24</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="L66" s="4" t="s">
         <v>683</v>
@@ -7015,19 +7036,19 @@
         <v>48</v>
       </c>
       <c r="O66" s="16" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="P66" s="16" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="Q66" s="16" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="R66" s="16" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>438</v>
       </c>
@@ -7059,10 +7080,10 @@
         <v>444</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="M67" s="7" t="s">
         <v>25</v>
@@ -7071,16 +7092,16 @@
         <v>445</v>
       </c>
       <c r="O67" s="16" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="P67" s="16" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="Q67" s="16" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="R67" s="16" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="175.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7127,16 +7148,16 @@
         <v>453</v>
       </c>
       <c r="O68" s="16" t="s">
+        <v>898</v>
+      </c>
+      <c r="P68" s="16" t="s">
+        <v>899</v>
+      </c>
+      <c r="Q68" s="16" t="s">
+        <v>900</v>
+      </c>
+      <c r="R68" s="16" t="s">
         <v>901</v>
-      </c>
-      <c r="P68" s="16" t="s">
-        <v>902</v>
-      </c>
-      <c r="Q68" s="16" t="s">
-        <v>903</v>
-      </c>
-      <c r="R68" s="16" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -7183,10 +7204,10 @@
         <v>563</v>
       </c>
       <c r="O69" s="16" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="P69" s="16" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="Q69" s="16" t="s">
         <v>783</v>
@@ -7195,7 +7216,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>457</v>
       </c>
@@ -7230,7 +7251,7 @@
         <v>688</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>670</v>
+        <v>986</v>
       </c>
       <c r="M70" s="7" t="s">
         <v>25</v>
@@ -7239,19 +7260,19 @@
         <v>445</v>
       </c>
       <c r="O70" s="16" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="P70" s="16" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="Q70" s="16" t="s">
-        <v>907</v>
+        <v>993</v>
       </c>
       <c r="R70" s="16" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>464</v>
       </c>
@@ -7295,10 +7316,10 @@
         <v>110</v>
       </c>
       <c r="O71" s="16" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="P71" s="16" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="Q71" s="16" t="s">
         <v>783</v>
@@ -7307,7 +7328,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>470</v>
       </c>
@@ -7342,7 +7363,7 @@
         <v>690</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>670</v>
+        <v>987</v>
       </c>
       <c r="M72" s="7" t="s">
         <v>25</v>
@@ -7351,19 +7372,19 @@
         <v>48</v>
       </c>
       <c r="O72" s="16" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="P72" s="16" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="Q72" s="16" t="s">
-        <v>911</v>
+        <v>994</v>
       </c>
       <c r="R72" s="16" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>477</v>
       </c>
@@ -7398,7 +7419,7 @@
         <v>691</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>670</v>
+        <v>988</v>
       </c>
       <c r="M73" s="7" t="s">
         <v>25</v>
@@ -7407,19 +7428,19 @@
         <v>48</v>
       </c>
       <c r="O73" s="16" t="s">
-        <v>867</v>
+        <v>989</v>
       </c>
       <c r="P73" s="16" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="Q73" s="16" t="s">
-        <v>867</v>
+        <v>995</v>
       </c>
       <c r="R73" s="16" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>484</v>
       </c>
@@ -7460,22 +7481,22 @@
         <v>25</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="O74" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P74" s="16" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="Q74" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R74" s="16" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>491</v>
       </c>
@@ -7489,7 +7510,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>94</v>
@@ -7516,22 +7537,22 @@
         <v>25</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="O75" s="16" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="P75" s="16" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="Q75" s="16" t="s">
-        <v>920</v>
+        <v>996</v>
       </c>
       <c r="R75" s="16" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>497</v>
       </c>
@@ -7575,19 +7596,19 @@
         <v>503</v>
       </c>
       <c r="O76" s="16" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="P76" s="16" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="Q76" s="16" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="R76" s="16" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" ht="91.2" x14ac:dyDescent="0.3">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>173</v>
       </c>
@@ -7595,13 +7616,13 @@
         <v>504</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>163</v>
@@ -7610,7 +7631,7 @@
         <v>505</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>33</v>
@@ -7628,22 +7649,22 @@
         <v>25</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="O77" s="16" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="P77" s="16" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="Q77" s="16" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="R77" s="16" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="216" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>506</v>
       </c>
@@ -7675,7 +7696,7 @@
         <v>512</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="L78" s="4" t="s">
         <v>687</v>
@@ -7687,19 +7708,19 @@
         <v>48</v>
       </c>
       <c r="O78" s="16" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="P78" s="16" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="Q78" s="16" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="R78" s="16" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>513</v>
       </c>
@@ -7743,19 +7764,19 @@
         <v>445</v>
       </c>
       <c r="O79" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P79" s="16" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="Q79" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R79" s="16" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" ht="45.6" x14ac:dyDescent="0.3">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="72" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>519</v>
       </c>
@@ -7790,7 +7811,7 @@
         <v>699</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="M80" s="7" t="s">
         <v>25</v>
@@ -7799,16 +7820,16 @@
         <v>525</v>
       </c>
       <c r="O80" s="16" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="P80" s="16" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="Q80" s="16" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="R80" s="16" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="129.6" x14ac:dyDescent="0.3">
@@ -7825,7 +7846,7 @@
         <v>19</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>70</v>
@@ -7852,19 +7873,19 @@
         <v>532</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="O81" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P81" s="16" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="Q81" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R81" s="16" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="115.2" x14ac:dyDescent="0.3">
@@ -7911,16 +7932,16 @@
         <v>48</v>
       </c>
       <c r="O82" s="16" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="P82" s="16" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="Q82" s="16" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="R82" s="16" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="230.4" x14ac:dyDescent="0.3">
@@ -7970,13 +7991,13 @@
         <v>761</v>
       </c>
       <c r="P83" s="16" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="Q83" s="16" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="R83" s="16" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="72" x14ac:dyDescent="0.3">
@@ -8023,16 +8044,16 @@
         <v>552</v>
       </c>
       <c r="O84" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P84" s="16" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="Q84" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="R84" s="16" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
   </sheetData>
@@ -8060,7 +8081,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -8181,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="E9" s="13">
         <f t="shared" si="0"/>
@@ -8199,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="E10" s="13">
         <f t="shared" si="0"/>
@@ -8457,20 +8478,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c76fba90-bd48-4e65-9fce-772627206c4f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c76fba90-bd48-4e65-9fce-772627206c4f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8493,14 +8514,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B903CEE-E95C-42FD-A969-F1901431EC77}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FB2A6B-D58A-4043-A4F7-532B34D9967F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -8515,4 +8528,12 @@
     <ds:schemaRef ds:uri="c76fba90-bd48-4e65-9fce-772627206c4f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B903CEE-E95C-42FD-A969-F1901431EC77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>